--- a/thesis_supporting_files/Phase1_ecosystem/Necessity_Domain_Matrix_v8.xlsx
+++ b/thesis_supporting_files/Phase1_ecosystem/Necessity_Domain_Matrix_v8.xlsx
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Coller FAIRR Protein Producer Index and Dow Jones Sustainability Index retained in the matrix but flagged 'out of scope as a demand': they rate large LISTED companies / index constituents; a 50-250 private SME is neither rated by nor able to join them, even aspirationally. So we do not score their 'disclosure topics' as demands. Kept visible as a directional investor-frontier signal only.</t>
+          <t>Coller FAIRR Protein Producer Index and Dow Jones Best-in-Class Indices retained in the matrix but flagged 'out of scope as a demand': they rate large LISTED companies / index constituents; a 50-250 private SME is neither rated by nor able to join them, even aspirationally. So we do not score their 'disclosure topics' as demands. Kept visible as a directional investor-frontier signal only.</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="29" t="inlineStr">
         <is>
-          <t>○  Dow Jones Sustainability Index (S&amp;P)</t>
+          <t>○  Dow Jones Best-in-Class Indices (S&amp;P)</t>
         </is>
       </c>
       <c r="B50" s="29" t="inlineStr">
@@ -5319,7 +5319,7 @@
 ●  UN Sustainable Development Goals
 ●  Move to Minus 15 [coalition; no disclosure requirement]
 ‡ Coller FAIRR Protein Producer Index [rated-not-actor — out of scope]
-‡ Dow Jones Sustainability Index (S&amp;P) [rated-not-actor — out of scope]</t>
+‡ Dow Jones Best-in-Class Indices (S&amp;P) [rated-not-actor — out of scope]</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>‡ Out of scope as a demand (retained for ecosystem completeness, NOT scored in Phase 3). Two reasons: RATED-NOT-ACTOR — investor benchmarks rating large listed firms only, SME neither rated nor joinable (Coller FAIRR, Dow Jones Sustainability Index); CANNOT-JOIN / benchmark — SeaBOS (keystone-company coalition, SME ineligible), GSSI (benchmark of schemes, obsolete). ISSF is conditional (tuna only). Their topic agendas are kept as a directional signal (e.g. FAIRR's protein-risk themes corroborate the GAP topics: AMU, feed, animal welfare) but impose no ratable disclosure demand.</t>
+          <t>‡ Out of scope as a demand (retained for ecosystem completeness, NOT scored in Phase 3). Two reasons: RATED-NOT-ACTOR — investor benchmarks rating large listed firms only, SME neither rated nor joinable (Coller FAIRR, Dow Jones Best-in-Class Indices); CANNOT-JOIN / benchmark — SeaBOS (keystone-company coalition, SME ineligible), GSSI (benchmark of schemes, obsolete). ISSF is conditional (tuna only). Their topic agendas are kept as a directional signal (e.g. FAIRR's protein-risk themes corroborate the GAP topics: AMU, feed, animal welfare) but impose no ratable disclosure demand.</t>
         </is>
       </c>
     </row>
@@ -8060,7 +8060,7 @@
     <row r="12" ht="23.25" customHeight="1">
       <c r="A12" s="77" t="inlineStr">
         <is>
-          <t>Dow Jones Sustainability Index (S&amp;P)</t>
+          <t>Dow Jones Best-in-Class Indices (S&amp;P)</t>
         </is>
       </c>
       <c r="B12" s="77" t="inlineStr">
